--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:18:10+00:00</t>
+    <t>2023-04-28T11:24:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:11+00:00</t>
+    <t>2023-04-28T11:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:31+00:00</t>
+    <t>2023-04-30T03:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:40+00:00</t>
+    <t>2023-04-30T03:44:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:58+00:00</t>
+    <t>2023-04-30T03:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:52:18+00:00</t>
+    <t>2023-04-30T03:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:53:51+00:00</t>
+    <t>2023-04-30T09:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T09:28:44+00:00</t>
+    <t>2023-05-01T08:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:52:03+00:00</t>
+    <t>2023-05-01T08:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:56:42+00:00</t>
+    <t>2023-05-01T09:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:10:15+00:00</t>
+    <t>2023-05-01T09:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:11:26+00:00</t>
+    <t>2023-05-01T09:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:13:53+00:00</t>
+    <t>2023-05-01T09:16:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:16:45+00:00</t>
+    <t>2023-05-01T16:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:06+00:00</t>
+    <t>2023-05-01T16:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:27+00:00</t>
+    <t>2023-05-01T18:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:00+00:00</t>
+    <t>2023-05-01T18:12:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:07+00:00</t>
+    <t>2023-05-02T21:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2173" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="415">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:42:53+00:00</t>
+    <t>2023-05-05T21:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1142,286 +1142,6 @@
   </si>
   <si>
     <t>./PrimaryAddress and ./OtherAddresses</t>
-  </si>
-  <si>
-    <t>Organization.address.id</t>
-  </si>
-  <si>
-    <t>Organization.address.extension</t>
-  </si>
-  <si>
-    <t>Organization.address.use</t>
-  </si>
-  <si>
-    <t>home | work | temp | old | billing - purpose of this address</t>
-  </si>
-  <si>
-    <t>The purpose of this address.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an address is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Allows an appropriate address to be chosen from a list of many.</t>
-  </si>
-  <si>
-    <t>home</t>
-  </si>
-  <si>
-    <t>The use of an address.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/address-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Address.use</t>
-  </si>
-  <si>
-    <t>XAD.7</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>./AddressPurpose</t>
-  </si>
-  <si>
-    <t>Organization.address.type</t>
-  </si>
-  <si>
-    <t>postal | physical | both</t>
-  </si>
-  <si>
-    <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
-  </si>
-  <si>
-    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
-  </si>
-  <si>
-    <t>both</t>
-  </si>
-  <si>
-    <t>The type of an address (physical / postal).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/address-type|4.0.1</t>
-  </si>
-  <si>
-    <t>Address.type</t>
-  </si>
-  <si>
-    <t>XAD.18</t>
-  </si>
-  <si>
-    <t>Organization.address.text</t>
-  </si>
-  <si>
-    <t>Text representation of the address</t>
-  </si>
-  <si>
-    <t>Specifies the entire address as it should be displayed e.g. on a postal label. This may be provided instead of or as well as the specific parts.</t>
-  </si>
-  <si>
-    <t>Can provide both a text representation and parts. Applications updating an address SHALL ensure that  when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
-  </si>
-  <si>
-    <t>A renderable, unencoded form.</t>
-  </si>
-  <si>
-    <t>137 Nowhere Street, Erewhon 9132</t>
-  </si>
-  <si>
-    <t>Address.text</t>
-  </si>
-  <si>
-    <t>XAD.1 + XAD.2 + XAD.3 + XAD.4 + XAD.5 + XAD.6</t>
-  </si>
-  <si>
-    <t>./formatted</t>
-  </si>
-  <si>
-    <t>Organization.address.line</t>
-  </si>
-  <si>
-    <t>Street name, number, direction &amp; P.O. Box etc.</t>
-  </si>
-  <si>
-    <t>This component contains the house number, apartment number, street name, street direction,  P.O. Box number, delivery hints, and similar address information.</t>
-  </si>
-  <si>
-    <t>137 Nowhere Street</t>
-  </si>
-  <si>
-    <t>Address.line</t>
-  </si>
-  <si>
-    <t>XAD.1 + XAD.2 (note: XAD.1 and XAD.2 have different meanings for a company address than for a person address)</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = AL]</t>
-  </si>
-  <si>
-    <t>./StreetAddress (newline delimitted)</t>
-  </si>
-  <si>
-    <t>Organization.address.city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municpality
-</t>
-  </si>
-  <si>
-    <t>Name of city, town etc.</t>
-  </si>
-  <si>
-    <t>The name of the city, town, suburb, village or other community or delivery center.</t>
-  </si>
-  <si>
-    <t>Erewhon</t>
-  </si>
-  <si>
-    <t>Address.city</t>
-  </si>
-  <si>
-    <t>XAD.3</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = CTY]</t>
-  </si>
-  <si>
-    <t>./Jurisdiction</t>
-  </si>
-  <si>
-    <t>Organization.address.district</t>
-  </si>
-  <si>
-    <t xml:space="preserve">County
-</t>
-  </si>
-  <si>
-    <t>District name (aka county)</t>
-  </si>
-  <si>
-    <t>The name of the administrative area (county).</t>
-  </si>
-  <si>
-    <t>District is sometimes known as county, but in some regions 'county' is used in place of city (municipality), so county name should be conveyed in city instead.</t>
-  </si>
-  <si>
-    <t>Madison</t>
-  </si>
-  <si>
-    <t>Address.district</t>
-  </si>
-  <si>
-    <t>XAD.9</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = CNT | CPA]</t>
-  </si>
-  <si>
-    <t>Organization.address.state</t>
-  </si>
-  <si>
-    <t>Province
-Territory</t>
-  </si>
-  <si>
-    <t>Sub-unit of country (abbreviations ok)</t>
-  </si>
-  <si>
-    <t>Sub-unit of a country with limited sovereignty in a federally organized country. A code may be used if codes are in common use (e.g. US 2 letter state codes).</t>
-  </si>
-  <si>
-    <t>Address.state</t>
-  </si>
-  <si>
-    <t>XAD.4</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = STA]</t>
-  </si>
-  <si>
-    <t>./Region</t>
-  </si>
-  <si>
-    <t>Organization.address.postalCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zip
-</t>
-  </si>
-  <si>
-    <t>Postal code for area</t>
-  </si>
-  <si>
-    <t>A postal code designating a region defined by the postal service.</t>
-  </si>
-  <si>
-    <t>9132</t>
-  </si>
-  <si>
-    <t>Address.postalCode</t>
-  </si>
-  <si>
-    <t>XAD.5</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = ZIP]</t>
-  </si>
-  <si>
-    <t>./PostalIdentificationCode</t>
-  </si>
-  <si>
-    <t>Organization.address.country</t>
-  </si>
-  <si>
-    <t>Country (e.g. can be ISO 3166 2 or 3 letter code)</t>
-  </si>
-  <si>
-    <t>Country - a nation as commonly understood or generally accepted.</t>
-  </si>
-  <si>
-    <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
-  </si>
-  <si>
-    <t>Address.country</t>
-  </si>
-  <si>
-    <t>XAD.6</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = CNT]</t>
-  </si>
-  <si>
-    <t>./Country</t>
-  </si>
-  <si>
-    <t>Organization.address.period</t>
-  </si>
-  <si>
-    <t>Time period when address was/is in use</t>
-  </si>
-  <si>
-    <t>Time period when address was/is in use.</t>
-  </si>
-  <si>
-    <t>Allows addresses to be placed in historical context.</t>
-  </si>
-  <si>
-    <t>&lt;valuePeriod xmlns="http://hl7.org/fhir"&gt;
-  &lt;start value="2010-03-23"/&gt;
-  &lt;end value="2010-07-01"/&gt;
-&lt;/valuePeriod&gt;</t>
-  </si>
-  <si>
-    <t>Address.period</t>
-  </si>
-  <si>
-    <t>XAD.12 / XAD.13 + XAD.14</t>
-  </si>
-  <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
   </si>
   <si>
     <t>Organization.partOf</t>
@@ -1878,7 +1598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN59"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.65625" customWidth="true" bestFit="true"/>
@@ -1900,7 +1620,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="39.97265625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -1916,7 +1636,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="45.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="218.1953125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6065,10 +5785,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -6193,19 +5913,21 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>160</v>
+        <v>301</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>161</v>
+        <v>366</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -6253,7 +5975,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>163</v>
+        <v>365</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6265,16 +5987,16 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>77</v>
+        <v>315</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6282,14 +6004,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6308,18 +6030,20 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>132</v>
+        <v>371</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>133</v>
+        <v>372</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>167</v>
+        <v>373</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6355,19 +6079,19 @@
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>171</v>
+        <v>370</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6379,13 +6103,13 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>164</v>
+        <v>376</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6396,10 +6120,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6416,26 +6140,22 @@
         <v>77</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>368</v>
+        <v>161</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6447,7 +6167,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -6459,13 +6179,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>373</v>
+        <v>77</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6483,7 +6203,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>375</v>
+        <v>163</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6495,16 +6215,16 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>377</v>
+        <v>164</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>378</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6512,21 +6232,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6535,19 +6255,19 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>380</v>
+        <v>133</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>381</v>
+        <v>167</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>382</v>
+        <v>135</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6561,7 +6281,7 @@
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>383</v>
+        <v>77</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -6573,13 +6293,13 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6597,25 +6317,25 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>386</v>
+        <v>171</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>387</v>
+        <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>377</v>
+        <v>164</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6626,45 +6346,45 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>391</v>
+        <v>135</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>392</v>
+        <v>141</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6677,7 +6397,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>393</v>
+        <v>77</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -6713,25 +6433,25 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>395</v>
+        <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>396</v>
+        <v>129</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6742,10 +6462,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6753,11 +6473,11 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6765,19 +6485,21 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6789,7 +6511,7 @@
         <v>77</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>400</v>
+        <v>77</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>77</v>
@@ -6801,13 +6523,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>77</v>
+        <v>389</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6825,13 +6547,13 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
@@ -6840,13 +6562,13 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>402</v>
+        <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>404</v>
+        <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6854,18 +6576,18 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>406</v>
+        <v>77</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>86</v>
@@ -6877,19 +6599,21 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>160</v>
+        <v>392</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
       </c>
@@ -6901,7 +6625,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -6937,7 +6661,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6952,13 +6676,13 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>413</v>
+        <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6966,21 +6690,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>415</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6989,21 +6713,21 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>160</v>
+        <v>344</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
@@ -7015,7 +6739,7 @@
         <v>77</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>419</v>
+        <v>77</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>77</v>
@@ -7051,13 +6775,13 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
@@ -7066,10 +6790,10 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7080,18 +6804,18 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>424</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>86</v>
@@ -7103,19 +6827,21 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>160</v>
+        <v>355</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7163,7 +6889,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>427</v>
+        <v>404</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7178,13 +6904,13 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>430</v>
+        <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7192,21 +6918,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>432</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -7215,19 +6941,21 @@
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>160</v>
+        <v>411</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
@@ -7239,7 +6967,7 @@
         <v>77</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>435</v>
+        <v>77</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>77</v>
@@ -7275,13 +7003,13 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
@@ -7290,1385 +7018,15 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>437</v>
+        <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>438</v>
+        <v>164</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>439</v>
+        <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN59" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -271,6 +271,9 @@
     <t>Organization(classCode=ORG, determinerCode=INST)</t>
   </si>
   <si>
+    <t>administrative.group</t>
+  </si>
+  <si>
     <t>Organization.id</t>
   </si>
   <si>
@@ -354,7 +357,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -412,6 +415,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -452,7 +459,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -512,205 +519,199 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Organization.identifier:XX.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:XX.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier:XX.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Organization.identifier:XX.type.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:XX.type.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:XX.type.coding</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:XX.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:XX.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:XX.type.coding.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Organization.identifier:XX.type.coding.version</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.version</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Organization.identifier:XX.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:XX.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier:XX.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier:XX.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:XX.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:XX.type.coding</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:XX.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:XX.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:XX.type.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Organization.identifier:XX.type.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.version</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -889,7 +890,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1176,6 +1177,10 @@
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>.contactParty</t>
@@ -1625,7 +1630,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.10546875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1873,15 +1878,15 @@
         <v>30</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1892,7 +1897,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -1901,19 +1906,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1963,13 +1968,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1992,10 +1997,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2006,7 +2011,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -2015,16 +2020,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2075,19 +2080,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2104,10 +2109,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2118,28 +2123,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2189,19 +2194,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2218,10 +2223,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2232,7 +2237,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2244,16 +2249,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2279,13 +2284,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2303,19 +2308,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2332,21 +2337,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2358,16 +2363,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2417,25 +2422,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2446,14 +2451,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2472,16 +2477,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2531,7 +2536,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2543,13 +2548,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2560,14 +2565,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2586,16 +2591,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2645,7 +2650,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2657,13 +2662,13 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2674,14 +2679,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2694,25 +2699,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2761,7 +2766,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2773,13 +2778,13 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2790,10 +2795,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2801,7 +2806,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
@@ -2813,20 +2818,20 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2863,19 +2868,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2884,43 +2889,43 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -2929,20 +2934,20 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2991,7 +2996,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3000,30 +3005,30 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3034,7 +3039,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -3046,13 +3051,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3103,13 +3108,13 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>77</v>
@@ -3121,7 +3126,7 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3132,14 +3137,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3158,16 +3163,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3205,19 +3210,19 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3229,13 +3234,13 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3246,10 +3251,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3260,31 +3265,31 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3309,11 +3314,9 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y15" t="s" s="2">
         <v>179</v>
       </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>180</v>
       </c>
@@ -3339,16 +3342,16 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>182</v>
@@ -3376,7 +3379,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3385,7 +3388,7 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>185</v>
@@ -3427,44 +3430,42 @@
       <c r="X16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>182</v>
@@ -3478,10 +3479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3492,7 +3493,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3504,13 +3505,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3561,13 +3562,13 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
@@ -3579,7 +3580,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3590,14 +3591,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3616,16 +3617,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3663,19 +3664,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3687,13 +3688,13 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3704,10 +3705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3727,22 +3728,22 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3791,7 +3792,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3803,13 +3804,13 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3820,10 +3821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3834,7 +3835,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3846,13 +3847,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3903,13 +3904,13 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
@@ -3921,7 +3922,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3932,14 +3933,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3958,16 +3959,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4005,19 +4006,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4029,13 +4030,13 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4046,10 +4047,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4060,7 +4061,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4069,22 +4070,22 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4094,64 +4095,64 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="T22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF22" t="s" s="2">
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK22" t="s" s="2">
+      <c r="AL22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4162,10 +4163,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4176,7 +4177,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4185,10 +4186,10 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>225</v>
@@ -4253,13 +4254,13 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>229</v>
@@ -4290,7 +4291,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4299,10 +4300,10 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>233</v>
@@ -4322,7 +4323,7 @@
         <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>77</v>
@@ -4367,13 +4368,13 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>237</v>
@@ -4404,7 +4405,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4413,10 +4414,10 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>241</v>
@@ -4481,13 +4482,13 @@
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>246</v>
@@ -4518,7 +4519,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4527,7 +4528,7 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>250</v>
@@ -4597,13 +4598,13 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>256</v>
@@ -4634,7 +4635,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4643,10 +4644,10 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>260</v>
@@ -4713,13 +4714,13 @@
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>266</v>
@@ -4747,10 +4748,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4759,10 +4760,10 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>270</v>
@@ -4829,13 +4830,13 @@
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>277</v>
@@ -4863,10 +4864,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4875,10 +4876,10 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>282</v>
@@ -4943,13 +4944,13 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>287</v>
@@ -4980,7 +4981,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -4989,7 +4990,7 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>292</v>
@@ -5055,13 +5056,13 @@
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>296</v>
@@ -5092,7 +5093,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5101,7 +5102,7 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>301</v>
@@ -5169,13 +5170,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>306</v>
@@ -5206,16 +5207,16 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>250</v>
@@ -5287,13 +5288,13 @@
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>315</v>
@@ -5333,7 +5334,7 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>185</v>
@@ -5409,7 +5410,7 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>327</v>
@@ -5418,7 +5419,7 @@
         <v>328</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>329</v>
@@ -5437,10 +5438,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5449,10 +5450,10 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>331</v>
@@ -5519,13 +5520,13 @@
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>335</v>
@@ -5568,7 +5569,7 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>339</v>
@@ -5641,7 +5642,7 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5904,7 +5905,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5913,7 +5914,7 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>301</v>
@@ -5981,13 +5982,13 @@
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>315</v>
@@ -5996,7 +5997,7 @@
         <v>369</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6103,13 +6104,13 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>376</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6120,10 +6121,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6134,7 +6135,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6146,13 +6147,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6203,13 +6204,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -6221,7 +6222,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6232,14 +6233,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6258,16 +6259,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6317,7 +6318,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6329,13 +6330,13 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6346,14 +6347,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6366,25 +6367,25 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6433,7 +6434,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6445,13 +6446,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6462,10 +6463,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6476,7 +6477,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6491,14 +6492,14 @@
         <v>185</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6526,10 +6527,10 @@
         <v>190</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6547,25 +6548,25 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6576,10 +6577,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6590,7 +6591,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6602,17 +6603,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6661,25 +6662,25 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6690,10 +6691,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6719,14 +6720,14 @@
         <v>344</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6775,7 +6776,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6787,13 +6788,13 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6804,10 +6805,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6818,7 +6819,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6833,14 +6834,14 @@
         <v>355</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6889,25 +6890,25 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6918,10 +6919,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6944,17 +6945,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7003,7 +7004,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7015,13 +7016,13 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="415">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -271,9 +271,6 @@
     <t>Organization(classCode=ORG, determinerCode=INST)</t>
   </si>
   <si>
-    <t>administrative.group</t>
-  </si>
-  <si>
     <t>Organization.id</t>
   </si>
   <si>
@@ -357,7 +354,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -415,10 +412,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -459,7 +452,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -519,6 +512,10 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -574,7 +571,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -608,6 +608,9 @@
     <t>extensible</t>
   </si>
   <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
@@ -708,10 +711,6 @@
     <t>Organization.identifier.type.coding.version</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -890,7 +889,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1177,10 +1176,6 @@
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>.contactParty</t>
@@ -1630,7 +1625,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.10546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1878,15 +1873,15 @@
         <v>30</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1897,28 +1892,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1968,13 +1963,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1997,10 +1992,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2011,25 +2006,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2080,19 +2075,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2109,10 +2104,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2123,28 +2118,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2194,19 +2189,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2223,10 +2218,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2237,7 +2232,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2249,16 +2244,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2284,43 +2279,43 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2337,21 +2332,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2363,16 +2358,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2422,25 +2417,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2451,14 +2446,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2477,16 +2472,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2536,7 +2531,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2548,13 +2543,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2565,14 +2560,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2591,16 +2586,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2650,7 +2645,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2662,13 +2657,13 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2679,14 +2674,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2699,25 +2694,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2766,7 +2761,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2778,13 +2773,13 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2795,10 +2790,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2806,7 +2801,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
@@ -2818,20 +2813,20 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2868,19 +2863,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="AC11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>152</v>
-      </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2889,65 +2884,65 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K12" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2996,7 +2991,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3005,30 +3000,30 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3039,7 +3034,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -3051,13 +3046,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3108,25 +3103,25 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3137,14 +3132,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3163,16 +3158,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3210,19 +3205,19 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AC14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AC14" t="s" s="2">
+      <c r="AD14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AD14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE14" t="s" s="2">
+      <c r="AF14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3234,13 +3229,13 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3251,10 +3246,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3265,31 +3260,31 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3314,9 +3309,11 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>180</v>
       </c>
@@ -3342,16 +3339,16 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>182</v>
@@ -3379,16 +3376,16 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>185</v>
@@ -3430,9 +3427,11 @@
       <c r="X16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3450,22 +3449,22 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>182</v>
@@ -3479,10 +3478,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3493,7 +3492,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3505,13 +3504,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3562,25 +3561,25 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3591,14 +3590,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3617,16 +3616,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3664,19 +3663,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3688,13 +3687,13 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3705,10 +3704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3728,22 +3727,22 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3792,7 +3791,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3804,13 +3803,13 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3821,10 +3820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3835,7 +3834,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3847,13 +3846,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3904,25 +3903,25 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3933,14 +3932,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3959,16 +3958,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4006,19 +4005,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AC21" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AC21" t="s" s="2">
+      <c r="AD21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE21" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AD21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE21" t="s" s="2">
+      <c r="AF21" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4030,13 +4029,13 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4047,10 +4046,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4061,31 +4060,31 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4095,7 +4094,7 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>77</v>
@@ -4134,25 +4133,25 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4163,10 +4162,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4177,19 +4176,19 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>225</v>
@@ -4254,13 +4253,13 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>229</v>
@@ -4291,19 +4290,19 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>233</v>
@@ -4323,7 +4322,7 @@
         <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>77</v>
@@ -4368,13 +4367,13 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>237</v>
@@ -4405,19 +4404,19 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>241</v>
@@ -4482,13 +4481,13 @@
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>246</v>
@@ -4519,16 +4518,16 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>250</v>
@@ -4598,13 +4597,13 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>256</v>
@@ -4635,19 +4634,19 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>260</v>
@@ -4714,13 +4713,13 @@
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>266</v>
@@ -4748,22 +4747,22 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>270</v>
@@ -4830,13 +4829,13 @@
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>277</v>
@@ -4864,22 +4863,22 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G29" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>282</v>
@@ -4944,13 +4943,13 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>287</v>
@@ -4981,16 +4980,16 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>292</v>
@@ -5056,13 +5055,13 @@
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>296</v>
@@ -5093,16 +5092,16 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>301</v>
@@ -5170,13 +5169,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>306</v>
@@ -5207,16 +5206,16 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>250</v>
@@ -5288,13 +5287,13 @@
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>315</v>
@@ -5334,7 +5333,7 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>185</v>
@@ -5410,7 +5409,7 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>327</v>
@@ -5419,7 +5418,7 @@
         <v>328</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>329</v>
@@ -5438,22 +5437,22 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K34" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>331</v>
@@ -5520,13 +5519,13 @@
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>335</v>
@@ -5569,7 +5568,7 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>339</v>
@@ -5642,7 +5641,7 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5905,16 +5904,16 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>301</v>
@@ -5982,13 +5981,13 @@
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>315</v>
@@ -5997,7 +5996,7 @@
         <v>369</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6104,13 +6103,13 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6121,10 +6120,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6135,7 +6134,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6147,13 +6146,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6204,25 +6203,25 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6233,14 +6232,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6259,16 +6258,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6318,7 +6317,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6330,13 +6329,13 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6347,14 +6346,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6367,25 +6366,25 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>383</v>
-      </c>
       <c r="N42" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6434,7 +6433,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6446,13 +6445,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6463,10 +6462,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6477,7 +6476,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6492,14 +6491,14 @@
         <v>185</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6527,46 +6526,46 @@
         <v>190</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6577,10 +6576,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6591,7 +6590,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6603,17 +6602,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6662,25 +6661,25 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6691,10 +6690,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6720,14 +6719,14 @@
         <v>344</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6776,7 +6775,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6788,13 +6787,13 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6805,10 +6804,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6819,7 +6818,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6834,14 +6833,14 @@
         <v>355</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6890,25 +6889,25 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6919,10 +6918,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6945,17 +6944,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7004,7 +7003,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7016,13 +7015,13 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-hiv-organization.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
